--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2362,8 +2490,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2376,616 +2508,659 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신고산 타령 — 민요채보-2/신고산 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">신고산 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="17"/>
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞
 汰</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="G4" s="20"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="19"/>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="19"/>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="19"/>
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 湳
 㳞</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="21"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="17"/>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">잠</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="17"/>
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-―
+      <c r="I7" s="18"/>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">無
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="3" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="E8" s="19"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="19"/>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲
 △</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">드</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="19"/>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 太
 無</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-―
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">仲
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="21"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 無</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞
 㳞</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="17"/>
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 △</t>
         </is>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="19"/>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="G13" s="19"/>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="16"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="G15" s="17"/>
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I15" s="17"/>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="16"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 太</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰
 太</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="20"/>
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="I16" s="20"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="16"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰
 㳞</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="20"/>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰
 㳞</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">집</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰
 㳞</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">차</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 △</t>
         </is>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="K17" s="19"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="16"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="G18" s="22"/>
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I53" s="2"/>
@@ -2760,13 +2760,13 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
@@ -2784,7 +2784,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -2870,7 +2870,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G7" s="8"/>
@@ -2938,7 +2938,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="9"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G9" s="9"/>
@@ -3012,7 +3012,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="I10" s="10"/>
@@ -3080,7 +3080,7 @@
       <c r="I12" s="9"/>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="9"/>
@@ -3145,7 +3145,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">無―</t>
+          <t xml:space="preserve">無–</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -3225,7 +3225,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2688,69 +2729,69 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">신고산 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌌다</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑汰</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">소리</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞潢</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2758,36 +2799,36 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2795,52 +2836,52 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太無</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2848,32 +2889,32 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="E6" s="27"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="28"/>
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2881,44 +2922,44 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">잠못드</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2926,28 +2967,28 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="B8" s="23"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="25"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -2955,40 +2996,40 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="B9" s="23"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南仲</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2996,65 +3037,65 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="E10" s="28"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="28"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="28"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="B11" s="23"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰애기</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우르르</t>
         </is>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3062,61 +3103,61 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="23"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="H13" s="23"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3124,53 +3165,53 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="23"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">반봇</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">함흥차</t>
         </is>
       </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -3178,57 +3219,57 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="B16" s="23"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="B17" s="23"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">짐짱</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">떠나는</t>
         </is>
       </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="H17" s="23"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3236,28 +3277,28 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="23"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="28"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="G18" s="28"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
+      <c r="K18" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -2712,22 +2712,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
       <c r="C9" s="25"/>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="K10" s="28"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
       <c r="C14" s="28"/>
@@ -3180,7 +3180,7 @@
       <c r="J14" s="23"/>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="29.14" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -3238,7 +3238,7 @@
       <c r="J16" s="23"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="28"/>

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -2727,7 +2727,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="43.99" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="29.14" customHeight="1">
+    <row r="3" ht="43.99" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2753,7 +2753,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">쌌다</t>
+          <t xml:space="preserve">쌌
+다</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -2763,7 +2764,8 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">소리</t>
+          <t xml:space="preserve">소
+리</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -2797,7 +2799,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="29.14" customHeight="1">
+    <row r="4" ht="43.99" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2834,7 +2836,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="29.14" customHeight="1">
+    <row r="5" ht="43.99" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2887,7 +2889,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="29.14" customHeight="1">
+    <row r="6" ht="43.99" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2920,7 +2922,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="29.14" customHeight="1">
+    <row r="7" ht="43.99" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2935,7 +2937,9 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">잠못드</t>
+          <t xml:space="preserve">잠
+못
+드</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -2965,7 +2969,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="29.14" customHeight="1">
+    <row r="8" ht="43.99" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -2994,7 +2998,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="29.14" customHeight="1">
+    <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
       <c r="C9" s="25"/>
@@ -3035,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="29.14" customHeight="1">
+    <row r="10" ht="43.99" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3064,7 +3068,7 @@
       </c>
       <c r="K10" s="28"/>
     </row>
-    <row r="11" ht="29.14" customHeight="1">
+    <row r="11" ht="43.99" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
@@ -3075,7 +3079,9 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">큰애기</t>
+          <t xml:space="preserve">큰
+애
+기</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -3085,7 +3091,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우르르</t>
+          <t xml:space="preserve">우
+르
+르</t>
         </is>
       </c>
       <c r="H11" s="23"/>
@@ -3101,7 +3109,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="29.14" customHeight="1">
+    <row r="12" ht="43.99" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
       <c r="C12" s="25"/>
@@ -3126,7 +3134,7 @@
       </c>
       <c r="K12" s="25"/>
     </row>
-    <row r="13" ht="29.14" customHeight="1">
+    <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -3163,7 +3171,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="29.14" customHeight="1">
+    <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
       <c r="C14" s="28"/>
@@ -3180,7 +3188,7 @@
       <c r="J14" s="23"/>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" ht="29.14" customHeight="1">
+    <row r="15" ht="43.99" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
@@ -3191,7 +3199,8 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">반봇</t>
+          <t xml:space="preserve">반
+봇</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -3201,7 +3210,9 @@
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">함흥차</t>
+          <t xml:space="preserve">함
+흥
+차</t>
         </is>
       </c>
       <c r="H15" s="23"/>
@@ -3217,7 +3228,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="29.14" customHeight="1">
+    <row r="16" ht="43.99" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -3238,7 +3249,7 @@
       <c r="J16" s="23"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="29.14" customHeight="1">
+    <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -3249,7 +3260,8 @@
       </c>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">짐짱</t>
+          <t xml:space="preserve">짐
+짱</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -3259,7 +3271,9 @@
       </c>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">떠나는</t>
+          <t xml:space="preserve">떠
+나
+는</t>
         </is>
       </c>
       <c r="H17" s="23"/>
@@ -3275,7 +3289,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="29.14" customHeight="1">
+    <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="28"/>

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2751,7 +2774,7 @@
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">쌌
 다</t>
@@ -2762,7 +2785,7 @@
           <t xml:space="preserve">姑汰</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">소
 리</t>
@@ -2773,7 +2796,7 @@
           <t xml:space="preserve">㳞潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">신</t>
         </is>
@@ -2783,7 +2806,7 @@
           <t xml:space="preserve">無潢</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -2793,7 +2816,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2806,31 +2829,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2843,7 +2866,7 @@
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -2853,7 +2876,7 @@
           <t xml:space="preserve">太無</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2863,7 +2886,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2873,7 +2896,7 @@
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -2883,7 +2906,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2896,27 +2919,27 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="23"/>
-      <c r="G6" s="28"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="28"/>
+      <c r="I6" s="34"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="28" t="inlineStr">
+      <c r="K6" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2929,13 +2952,13 @@
           <t xml:space="preserve">／</t>
         </is>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">잠
 못
@@ -2947,13 +2970,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G7" s="24"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2963,7 +2986,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -2972,27 +2995,27 @@
     <row r="8" ht="43.99" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="23"/>
-      <c r="G8" s="25"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3001,13 +3024,13 @@
     <row r="9" ht="43.99" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="25"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南仲</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -3017,13 +3040,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3033,7 +3056,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3046,38 +3069,38 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="28"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="23"/>
-      <c r="G10" s="28"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="I10" s="28"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="34"/>
     </row>
     <row r="11" ht="43.99" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無無</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">큰
 애
@@ -3089,7 +3112,7 @@
           <t xml:space="preserve">潢仲</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 르
@@ -3097,13 +3120,13 @@
         </is>
       </c>
       <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3112,38 +3135,38 @@
     <row r="12" ht="43.99" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="23"/>
-      <c r="I12" s="25"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="31"/>
     </row>
     <row r="13" ht="43.99" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -3153,19 +3176,19 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">르</t>
         </is>
       </c>
       <c r="H13" s="23"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3174,30 +3197,30 @@
     <row r="14" ht="43.99" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="23"/>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="23"/>
-      <c r="I14" s="28"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="23"/>
-      <c r="K14" s="28"/>
+      <c r="K14" s="34"/>
     </row>
     <row r="15" ht="43.99" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無–</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">반
 봇</t>
@@ -3208,7 +3231,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">함
 흥
@@ -3216,13 +3239,13 @@
         </is>
       </c>
       <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="30"/>
       <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K15" s="24" t="inlineStr">
+      <c r="K15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -3231,34 +3254,34 @@
     <row r="16" ht="43.99" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="23"/>
-      <c r="I16" s="25"/>
+      <c r="I16" s="31"/>
       <c r="J16" s="23"/>
-      <c r="K16" s="25"/>
+      <c r="K16" s="31"/>
     </row>
     <row r="17" ht="43.99" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="25"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">짐
 짱</t>
@@ -3269,7 +3292,7 @@
           <t xml:space="preserve">仲潢</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">떠
 나
@@ -3277,13 +3300,13 @@
         </is>
       </c>
       <c r="H17" s="23"/>
-      <c r="I17" s="25"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3292,27 +3315,27 @@
     <row r="18" ht="43.99" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="28"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E18" s="28"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G18" s="28"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="23"/>
-      <c r="I18" s="28"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K18" s="28"/>
+      <c r="K18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -2012,6 +2012,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2026,10 +2029,10 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="102.95" customHeight="1">
+    <row r="2" ht="52.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2046,7 +2049,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="102.95" customHeight="1">
+    <row r="3" ht="117.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2114,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102.95" customHeight="1">
+    <row r="4" ht="117.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2177,7 +2180,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="102.95" customHeight="1">
+    <row r="5" ht="117.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -2231,7 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="102.95" customHeight="1">
+    <row r="6" ht="117.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="24" t="inlineStr">
         <is>
@@ -2284,7 +2287,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="102.95" customHeight="1">
+    <row r="7" ht="117.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2334,7 +2337,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="102.95" customHeight="1">
+    <row r="8" ht="117.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2376,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="102.95" customHeight="1">
+    <row r="9" ht="117.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2424,7 +2427,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="102.95" customHeight="1">
+    <row r="10" ht="117.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="27"/>
@@ -2480,6 +2483,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신고산 타령.xlsx
+++ b/sheets/민요/검수/신고산 타령.xlsx
@@ -2017,15 +2017,15 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
